--- a/docs/downloads/13/tbl_codes_aberrants_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/13/tbl_codes_aberrants_alaotra_feramanga_atsimo.xlsx
@@ -351,13 +351,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>j5</t>
+          <t>Obs_n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -367,25 +367,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Enqueteur</t>
+          <t>j11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Hameau</t>
+          <t>qual1aa</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>j11</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>qual1aa</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>qual2aa</t>
         </is>
@@ -393,7 +383,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2133035</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -402,29 +392,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Analamiranga</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2111000</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -432,16 +412,6 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Avaradrano</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
@@ -449,7 +419,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2121035</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -458,29 +428,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Mangabe</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>Bonne</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="E4">
         <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2111242</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -489,29 +449,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E29</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Avaradrano</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>Bonne</t>
         </is>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2121017</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -520,23 +470,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E29</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mangabe</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>Bonne</t>
         </is>
       </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
     </row>
